--- a/yang-diujikan/ips - kunci.xlsx
+++ b/yang-diujikan/ips - kunci.xlsx
@@ -1,22 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dokumen\PERANGKAT K13\SMP\US\fix\Soal US SMP - IPS (Websiteedukasi.com)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Semester PKBM\yang-diujikan\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC0D435-9FD1-4429-8F31-5F79E0F2D10A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="37710" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -275,7 +284,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -644,6 +653,33 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -665,35 +701,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -788,6 +797,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -823,6 +849,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -998,7 +1041,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1017,67 +1060,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
       <c r="L1" s="20"/>
     </row>
     <row r="2" spans="1:12" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
       <c r="L2" s="22"/>
     </row>
     <row r="3" spans="1:12" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
       <c r="L3" s="20"/>
     </row>
     <row r="4" spans="1:12" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
       <c r="L4" s="20"/>
     </row>
     <row r="5" spans="1:12" s="21" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1097,18 +1140,18 @@
       <c r="L5" s="20"/>
     </row>
     <row r="6" spans="1:12" s="21" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43" t="s">
+      <c r="B6" s="34"/>
+      <c r="C6" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43" t="s">
+      <c r="D6" s="34"/>
+      <c r="E6" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="43"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="26"/>
       <c r="H6" s="26"/>
       <c r="I6" s="26"/>
@@ -1117,18 +1160,18 @@
       <c r="L6" s="20"/>
     </row>
     <row r="7" spans="1:12" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45">
+      <c r="B7" s="35"/>
+      <c r="C7" s="36">
         <v>40</v>
       </c>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45">
+      <c r="D7" s="36"/>
+      <c r="E7" s="36">
         <v>60</v>
       </c>
-      <c r="F7" s="45"/>
+      <c r="F7" s="36"/>
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
       <c r="I7" s="26"/>
@@ -1137,18 +1180,18 @@
       <c r="L7" s="20"/>
     </row>
     <row r="8" spans="1:12" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45">
+      <c r="B8" s="35"/>
+      <c r="C8" s="36">
         <v>5</v>
       </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45">
+      <c r="D8" s="36"/>
+      <c r="E8" s="36">
         <v>40</v>
       </c>
-      <c r="F8" s="45"/>
+      <c r="F8" s="36"/>
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
       <c r="I8" s="26"/>
@@ -1157,17 +1200,17 @@
       <c r="L8" s="20"/>
     </row>
     <row r="9" spans="1:12" s="21" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
       <c r="L9" s="20"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -1233,7 +1276,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" s="25" t="s">
         <v>13</v>
@@ -1464,28 +1507,28 @@
     </row>
     <row r="22" spans="1:12" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
     </row>
     <row r="24" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A24" s="39" t="s">
+      <c r="A24" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="39"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
@@ -1493,7 +1536,7 @@
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
-      <c r="D25" s="38" t="s">
+      <c r="D25" s="37" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1503,7 +1546,7 @@
       </c>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
-      <c r="D26" s="38"/>
+      <c r="D26" s="37"/>
     </row>
     <row r="27" spans="1:12" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2"/>
@@ -2028,36 +2071,36 @@
       <c r="H40" s="2"/>
     </row>
     <row r="41" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="36" t="s">
+      <c r="A41" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="36"/>
-      <c r="K41" s="36"/>
-      <c r="L41" s="36"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="45"/>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="45"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="45"/>
     </row>
     <row r="42" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="37" t="s">
+      <c r="A42" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="37"/>
-      <c r="K42" s="37"/>
-      <c r="L42" s="37"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="46"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="46"/>
+      <c r="K42" s="46"/>
+      <c r="L42" s="46"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="18"/>
@@ -2074,19 +2117,19 @@
       <c r="L43" s="18"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="35" t="s">
+      <c r="A44" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="35"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="35"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44"/>
     </row>
     <row r="45" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
@@ -2122,15 +2165,15 @@
         <f>(D46/B46*C46)</f>
         <v>0</v>
       </c>
-      <c r="G46" s="47" t="s">
+      <c r="G46" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="H46" s="47"/>
+      <c r="H46" s="39"/>
       <c r="I46" s="13" t="s">
         <v>57</v>
       </c>
       <c r="J46" s="13"/>
-      <c r="K46" s="47" t="s">
+      <c r="K46" s="39" t="s">
         <v>61</v>
       </c>
       <c r="L46" s="14"/>
@@ -2152,13 +2195,13 @@
         <f t="shared" ref="E47:E50" si="4">(D47/B47*C47)</f>
         <v>0</v>
       </c>
-      <c r="G47" s="47"/>
-      <c r="H47" s="47"/>
+      <c r="G47" s="39"/>
+      <c r="H47" s="39"/>
       <c r="I47" s="14" t="s">
         <v>58</v>
       </c>
       <c r="J47" s="14"/>
-      <c r="K47" s="47"/>
+      <c r="K47" s="39"/>
       <c r="L47" s="14"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
@@ -2226,13 +2269,13 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="32" t="s">
+      <c r="A51" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="33"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="34"/>
+      <c r="B51" s="42"/>
+      <c r="C51" s="42"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="43"/>
     </row>
     <row r="52" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="9"/>
@@ -2261,13 +2304,13 @@
     <row r="54" spans="1:12" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="28"/>
     </row>
-    <row r="55" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="38" t="s">
+    <row r="55" spans="1:12" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="37" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="38"/>
-      <c r="C55" s="38"/>
-      <c r="D55" s="46"/>
+      <c r="B55" s="37"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="38"/>
       <c r="E55" s="12">
         <f>(E52*40/100)</f>
         <v>0</v>
@@ -2275,23 +2318,35 @@
     </row>
     <row r="56" spans="1:12" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="57" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="40" t="s">
+      <c r="A57" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B57" s="41"/>
-      <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="41"/>
-      <c r="J57" s="41"/>
-      <c r="K57" s="41"/>
-      <c r="L57" s="42"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A57:L57"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:D6"/>
@@ -2305,18 +2360,6 @@
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="K46:K47"/>
     <mergeCell ref="G46:H47"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A41:L41"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="A24:H24"/>
   </mergeCells>
   <pageMargins left="0.51181102362204722" right="0.19685039370078741" top="0.35433070866141736" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="90" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -2324,7 +2367,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2333,7 +2376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
